--- a/astro-site/public/dl/fine-dining-checklist-templates/07-chefs-table-special-events-checklist.xlsx
+++ b/astro-site/public/dl/fine-dining-checklist-templates/07-chefs-table-special-events-checklist.xlsx
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Select the location and check the facilities (water, power, gas)</t>
+          <t>Select the location and check the facilities (water, power, gas); temporary food event permit and health department approval; handwashing station and hot / cold holding on site</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
